--- a/precos.xlsx
+++ b/precos.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Usuários Locais\Fellipe\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Usuários Locais\Fellipe\Desktop\bot-telegram\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -35,9 +35,6 @@
     <t>Preco</t>
   </si>
   <si>
-    <t>iphone11</t>
-  </si>
-  <si>
     <t>a12</t>
   </si>
   <si>
@@ -45,6 +42,9 @@
   </si>
   <si>
     <t>bateria</t>
+  </si>
+  <si>
+    <t>iphone 11</t>
   </si>
 </sst>
 </file>
@@ -383,10 +383,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2">
         <v>250</v>
@@ -394,10 +394,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3">
         <v>120</v>
@@ -405,10 +405,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
         <v>4</v>
-      </c>
-      <c r="B4" t="s">
-        <v>5</v>
       </c>
       <c r="C4">
         <v>180</v>

--- a/precos.xlsx
+++ b/precos.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="8">
   <si>
     <t>Modelo</t>
   </si>
@@ -32,9 +32,6 @@
     <t>Servico</t>
   </si>
   <si>
-    <t>Preco</t>
-  </si>
-  <si>
     <t>a12</t>
   </si>
   <si>
@@ -45,6 +42,12 @@
   </si>
   <si>
     <t>iphone 11</t>
+  </si>
+  <si>
+    <t>PrecoVista</t>
+  </si>
+  <si>
+    <t>PrecoCartao</t>
   </si>
 </sst>
 </file>
@@ -362,15 +365,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -378,40 +382,52 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>6</v>
+      </c>
+      <c r="D1" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C2">
         <v>250</v>
       </c>
+      <c r="D2">
+        <v>270</v>
+      </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>120</v>
+        <v>140</v>
+      </c>
+      <c r="D3">
+        <v>160</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>4</v>
-      </c>
       <c r="C4">
-        <v>180</v>
+        <v>170</v>
+      </c>
+      <c r="D4">
+        <v>187</v>
       </c>
     </row>
   </sheetData>

--- a/precos.xlsx
+++ b/precos.xlsx
@@ -43,10 +43,10 @@
     <t xml:space="preserve">bateria</t>
   </si>
   <si>
-    <t xml:space="preserve">A12 – sem aro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A12 – com aro</t>
+    <t xml:space="preserve">a12 – sem aro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a12 – com aro</t>
   </si>
 </sst>
 </file>

--- a/precos.xlsx
+++ b/precos.xlsx
@@ -43,10 +43,10 @@
     <t xml:space="preserve">bateria</t>
   </si>
   <si>
-    <t xml:space="preserve">a12 – sem aro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">a12 – com aro</t>
+    <t xml:space="preserve">a12 sem aro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a12 com aro</t>
   </si>
 </sst>
 </file>

--- a/precos.xlsx
+++ b/precos.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="13">
   <si>
     <t xml:space="preserve">Modelo</t>
   </si>
@@ -28,6 +28,9 @@
     <t xml:space="preserve">Servico</t>
   </si>
   <si>
+    <t xml:space="preserve">TipoAro</t>
+  </si>
+  <si>
     <t xml:space="preserve">PrecoVista</t>
   </si>
   <si>
@@ -40,13 +43,22 @@
     <t xml:space="preserve">tela</t>
   </si>
   <si>
+    <t xml:space="preserve">padrao</t>
+  </si>
+  <si>
     <t xml:space="preserve">bateria</t>
   </si>
   <si>
     <t xml:space="preserve">a12 sem aro</t>
   </si>
   <si>
+    <t xml:space="preserve">sem aro</t>
+  </si>
+  <si>
     <t xml:space="preserve">a12 com aro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">com aro</t>
   </si>
 </sst>
 </file>
@@ -122,8 +134,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -316,82 +332,97 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="7.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="10.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="11.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="7.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="10.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="11.71"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="0" t="n">
+      <c r="B2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="1" t="n">
         <v>260</v>
       </c>
-      <c r="D2" s="0" t="n">
+      <c r="E2" s="1" t="n">
         <v>290</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="0" t="n">
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="1" t="n">
         <v>220</v>
       </c>
-      <c r="D3" s="0" t="n">
+      <c r="E3" s="1" t="n">
         <v>240</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="0" t="n">
+      <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="1" t="n">
         <v>170</v>
       </c>
-      <c r="D4" s="0" t="n">
+      <c r="E4" s="1" t="n">
         <v>186</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="0" t="n">
+      <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="1" t="n">
         <v>190</v>
       </c>
-      <c r="D5" s="0" t="n">
+      <c r="E5" s="1" t="n">
         <v>209</v>
       </c>
     </row>

--- a/precos.xlsx
+++ b/precos.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="12">
   <si>
     <t xml:space="preserve">Modelo</t>
   </si>
@@ -49,13 +49,10 @@
     <t xml:space="preserve">bateria</t>
   </si>
   <si>
-    <t xml:space="preserve">a12 sem aro</t>
+    <t xml:space="preserve">a12</t>
   </si>
   <si>
     <t xml:space="preserve">sem aro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">a12 com aro</t>
   </si>
   <si>
     <t xml:space="preserve">com aro</t>
@@ -411,13 +408,13 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>190</v>

--- a/precos.xlsx
+++ b/precos.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="24">
   <si>
     <t xml:space="preserve">Modelo</t>
   </si>
@@ -56,6 +56,42 @@
   </si>
   <si>
     <t xml:space="preserve">com aro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iphone xr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iphone 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iphone 6s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iphone 6 plus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iphone 6s plus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iphone 7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iphone 8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iphone 7 plus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iphone 8 plus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iphone x</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1ª linha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">oled</t>
   </si>
 </sst>
 </file>
@@ -329,7 +365,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15.16"/>
@@ -423,6 +459,193 @@
         <v>209</v>
       </c>
     </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>260</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>150</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>160</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>170</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>170</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>160</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>160</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>190</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>190</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>240</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>290</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>320</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.511805555555556" right="0.511805555555556" top="0.7875" bottom="0.7875" header="0.511811023622047" footer="0.511811023622047"/>

--- a/precos.xlsx
+++ b/precos.xlsx
@@ -76,13 +76,13 @@
     <t xml:space="preserve">Iphone 7</t>
   </si>
   <si>
-    <t xml:space="preserve">Iphone 8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Iphone 7 plus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Iphone 8 plus</t>
+    <t xml:space="preserve">iphone 8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iphone 7 plus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iphone 8 plus</t>
   </si>
   <si>
     <t xml:space="preserve">iphone x</t>

--- a/precos.xlsx
+++ b/precos.xlsx
@@ -28,7 +28,7 @@
     <t xml:space="preserve">Servico</t>
   </si>
   <si>
-    <t xml:space="preserve">TipoAro</t>
+    <t xml:space="preserve">Variacao</t>
   </si>
   <si>
     <t xml:space="preserve">PrecoVista</t>

--- a/precos.xlsx
+++ b/precos.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="28">
   <si>
     <t xml:space="preserve">Modelo</t>
   </si>
@@ -61,6 +61,12 @@
     <t xml:space="preserve">iphone xr</t>
   </si>
   <si>
+    <t xml:space="preserve">1ª linha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">oled</t>
+  </si>
+  <si>
     <t xml:space="preserve">Iphone 6</t>
   </si>
   <si>
@@ -88,10 +94,16 @@
     <t xml:space="preserve">iphone x</t>
   </si>
   <si>
-    <t xml:space="preserve">1ª linha</t>
-  </si>
-  <si>
-    <t xml:space="preserve">oled</t>
+    <t xml:space="preserve">iphone xs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iphone xs max</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iphone 11 pro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iphone 11 pro max</t>
   </si>
 </sst>
 </file>
@@ -365,10 +377,10 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="17.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="7.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="10.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="11.71"/>
@@ -467,35 +479,35 @@
         <v>6</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D6" s="1" t="n">
+        <v>230</v>
+      </c>
+      <c r="E6" s="1" t="n">
         <v>260</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>280</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>150</v>
+        <v>290</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>165</v>
+        <v>320</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>6</v>
@@ -504,15 +516,15 @@
         <v>7</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>175</v>
+        <v>165</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>6</v>
@@ -521,15 +533,15 @@
         <v>7</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>186</v>
+        <v>175</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>6</v>
@@ -546,7 +558,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>6</v>
@@ -555,15 +567,15 @@
         <v>7</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>176</v>
+        <v>186</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>6</v>
@@ -580,7 +592,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>6</v>
@@ -589,15 +601,15 @@
         <v>7</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>210</v>
+        <v>176</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>6</v>
@@ -614,36 +626,189 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>240</v>
+        <v>190</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>260</v>
+        <v>210</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>240</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D16" s="1" t="n">
+      <c r="B17" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17" s="1" t="n">
         <v>290</v>
       </c>
-      <c r="E16" s="1" t="n">
+      <c r="E17" s="1" t="n">
         <v>320</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>240</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>290</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>260</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>540</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>330</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>480</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>380</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>570</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>620</v>
       </c>
     </row>
   </sheetData>

--- a/precos.xlsx
+++ b/precos.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="42">
   <si>
     <t xml:space="preserve">Modelo</t>
   </si>
@@ -104,6 +104,48 @@
   </si>
   <si>
     <t xml:space="preserve">iphone 11 pro max</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iphone 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iphone 12 pro max</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iphone 13 pro max</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iphone 14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">zb631kl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">zc551kl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">zc553kl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">zc500tg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">zd552kl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ze520kl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ze551kl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ze620kl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">zb634kl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">k10</t>
   </si>
 </sst>
 </file>
@@ -377,7 +419,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="17.29"/>
@@ -811,6 +853,312 @@
         <v>620</v>
       </c>
     </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D26" s="1" t="n">
+        <v>270</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>500</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D29" s="1" t="n">
+        <v>450</v>
+      </c>
+      <c r="E29" s="1" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D30" s="1" t="n">
+        <v>550</v>
+      </c>
+      <c r="E30" s="1" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D31" s="1" t="n">
+        <v>260</v>
+      </c>
+      <c r="E31" s="1" t="n">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D32" s="1" t="n">
+        <v>360</v>
+      </c>
+      <c r="E32" s="1" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D33" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="E33" s="1" t="n">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D34" s="1" t="n">
+        <v>280</v>
+      </c>
+      <c r="E34" s="1" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D35" s="1" t="n">
+        <v>160</v>
+      </c>
+      <c r="E35" s="1" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D36" s="1" t="n">
+        <v>190</v>
+      </c>
+      <c r="E36" s="1" t="n">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D37" s="1" t="n">
+        <v>160</v>
+      </c>
+      <c r="E37" s="1" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D38" s="1" t="n">
+        <v>340</v>
+      </c>
+      <c r="E38" s="1" t="n">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D39" s="1" t="n">
+        <v>230</v>
+      </c>
+      <c r="E39" s="1" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D40" s="1" t="n">
+        <v>160</v>
+      </c>
+      <c r="E40" s="1" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D41" s="1" t="n">
+        <v>280</v>
+      </c>
+      <c r="E41" s="1" t="n">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D42" s="1" t="n">
+        <v>250</v>
+      </c>
+      <c r="E42" s="1" t="n">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D43" s="1" t="n">
+        <v>160</v>
+      </c>
+      <c r="E43" s="1" t="n">
+        <v>175</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.511805555555556" right="0.511805555555556" top="0.7875" bottom="0.7875" header="0.511811023622047" footer="0.511811023622047"/>

--- a/precos.xlsx
+++ b/precos.xlsx
@@ -22,19 +22,19 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="42">
   <si>
-    <t xml:space="preserve">Modelo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Servico</t>
+    <t xml:space="preserve">modelo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">servico</t>
   </si>
   <si>
     <t xml:space="preserve">Variacao</t>
   </si>
   <si>
-    <t xml:space="preserve">PrecoVista</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PrecoCartao</t>
+    <t xml:space="preserve">precovista</t>
+  </si>
+  <si>
+    <t xml:space="preserve">precocartao</t>
   </si>
   <si>
     <t xml:space="preserve">iphone 11</t>
@@ -155,7 +155,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -177,6 +177,14 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -221,12 +229,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -429,19 +441,19 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
     </row>

--- a/precos.xlsx
+++ b/precos.xlsx
@@ -22,19 +22,19 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="42">
   <si>
-    <t xml:space="preserve">modelo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">servico</t>
+    <t xml:space="preserve">Modelo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Servico</t>
   </si>
   <si>
     <t xml:space="preserve">Variacao</t>
   </si>
   <si>
-    <t xml:space="preserve">precovista</t>
-  </si>
-  <si>
-    <t xml:space="preserve">precocartao</t>
+    <t xml:space="preserve">PrecoVista</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PrecoCartao</t>
   </si>
   <si>
     <t xml:space="preserve">iphone 11</t>

--- a/precos.xlsx
+++ b/precos.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="48">
   <si>
     <t xml:space="preserve">Modelo</t>
   </si>
@@ -146,6 +146,24 @@
   </si>
   <si>
     <t xml:space="preserve">k10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">k10 TV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K10 2017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">k10 pro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">k10 power</t>
+  </si>
+  <si>
+    <t xml:space="preserve">k11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">k11 plis</t>
   </si>
 </sst>
 </file>
@@ -431,7 +449,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="17.29"/>
@@ -1171,6 +1189,108 @@
         <v>175</v>
       </c>
     </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D44" s="1" t="n">
+        <v>190</v>
+      </c>
+      <c r="E44" s="1" t="n">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D45" s="1" t="n">
+        <v>190</v>
+      </c>
+      <c r="E45" s="1" t="n">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D46" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="E46" s="1" t="n">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D47" s="1" t="n">
+        <v>180</v>
+      </c>
+      <c r="E47" s="1" t="n">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D48" s="1" t="n">
+        <v>190</v>
+      </c>
+      <c r="E48" s="1" t="n">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D49" s="1" t="n">
+        <v>190</v>
+      </c>
+      <c r="E49" s="1" t="n">
+        <v>209</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.511805555555556" right="0.511805555555556" top="0.7875" bottom="0.7875" header="0.511811023622047" footer="0.511811023622047"/>

--- a/precos.xlsx
+++ b/precos.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="56">
   <si>
     <t xml:space="preserve">Modelo</t>
   </si>
@@ -163,7 +163,31 @@
     <t xml:space="preserve">k11</t>
   </si>
   <si>
-    <t xml:space="preserve">k11 plis</t>
+    <t xml:space="preserve">k11 plus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">k12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">k12 plus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">k40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">k22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">k40s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">k41s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">k12 max</t>
+  </si>
+  <si>
+    <t xml:space="preserve">k12 prime</t>
   </si>
 </sst>
 </file>
@@ -449,7 +473,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:E60"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="17.29"/>
@@ -1291,6 +1315,193 @@
         <v>209</v>
       </c>
     </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D50" s="1" t="n">
+        <v>180</v>
+      </c>
+      <c r="E50" s="1" t="n">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D51" s="1" t="n">
+        <v>180</v>
+      </c>
+      <c r="E51" s="1" t="n">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D52" s="1" t="n">
+        <v>180</v>
+      </c>
+      <c r="E52" s="1" t="n">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D53" s="1" t="n">
+        <v>170</v>
+      </c>
+      <c r="E53" s="1" t="n">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D54" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="E54" s="1" t="n">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D55" s="1" t="n">
+        <v>180</v>
+      </c>
+      <c r="E55" s="1" t="n">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D56" s="1" t="n">
+        <v>210</v>
+      </c>
+      <c r="E56" s="1" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D57" s="1" t="n">
+        <v>180</v>
+      </c>
+      <c r="E57" s="1" t="n">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D58" s="1" t="n">
+        <v>210</v>
+      </c>
+      <c r="E58" s="1" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D59" s="1" t="n">
+        <v>180</v>
+      </c>
+      <c r="E59" s="1" t="n">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D60" s="1" t="n">
+        <v>180</v>
+      </c>
+      <c r="E60" s="1" t="n">
+        <v>198</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.511805555555556" right="0.511805555555556" top="0.7875" bottom="0.7875" header="0.511811023622047" footer="0.511811023622047"/>

--- a/precos.xlsx
+++ b/precos.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="66">
   <si>
     <t xml:space="preserve">Modelo</t>
   </si>
@@ -188,6 +188,36 @@
   </si>
   <si>
     <t xml:space="preserve">k12 prime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">k50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">k50s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">k51s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">k42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">k52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">k62</t>
+  </si>
+  <si>
+    <t xml:space="preserve">k61</t>
+  </si>
+  <si>
+    <t xml:space="preserve">k8 plus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">k9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tecno spark 10 pro</t>
   </si>
 </sst>
 </file>
@@ -473,7 +503,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E60"/>
+  <dimension ref="A1:E75"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="17.29"/>
@@ -1502,6 +1532,261 @@
         <v>198</v>
       </c>
     </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D61" s="1" t="n">
+        <v>180</v>
+      </c>
+      <c r="E61" s="1" t="n">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D62" s="1" t="n">
+        <v>180</v>
+      </c>
+      <c r="E62" s="1" t="n">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D63" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="E63" s="1" t="n">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D64" s="1" t="n">
+        <v>180</v>
+      </c>
+      <c r="E64" s="1" t="n">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D65" s="1" t="n">
+        <v>210</v>
+      </c>
+      <c r="E65" s="1" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D66" s="1" t="n">
+        <v>180</v>
+      </c>
+      <c r="E66" s="1" t="n">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D67" s="1" t="n">
+        <v>230</v>
+      </c>
+      <c r="E67" s="1" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D68" s="1" t="n">
+        <v>180</v>
+      </c>
+      <c r="E68" s="1" t="n">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D69" s="1" t="n">
+        <v>180</v>
+      </c>
+      <c r="E69" s="1" t="n">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D70" s="1" t="n">
+        <v>230</v>
+      </c>
+      <c r="E70" s="1" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D71" s="1" t="n">
+        <v>190</v>
+      </c>
+      <c r="E71" s="1" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D72" s="1" t="n">
+        <v>250</v>
+      </c>
+      <c r="E72" s="1" t="n">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D73" s="1" t="n">
+        <v>180</v>
+      </c>
+      <c r="E73" s="1" t="n">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D74" s="1" t="n">
+        <v>180</v>
+      </c>
+      <c r="E74" s="1" t="n">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D75" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="E75" s="1" t="n">
+        <v>240</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.511805555555556" right="0.511805555555556" top="0.7875" bottom="0.7875" header="0.511811023622047" footer="0.511811023622047"/>

--- a/precos.xlsx
+++ b/precos.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="72">
   <si>
     <t xml:space="preserve">Modelo</t>
   </si>
@@ -218,6 +218,24 @@
   </si>
   <si>
     <t xml:space="preserve">tecno spark 10 pro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">e20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">e22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">e32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">g22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">e30</t>
   </si>
 </sst>
 </file>
@@ -503,7 +521,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E75"/>
+  <dimension ref="A1:E87"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="17.29"/>
@@ -1787,6 +1805,198 @@
         <v>240</v>
       </c>
     </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D76" s="1" t="n">
+        <v>190</v>
+      </c>
+      <c r="E76" s="1" t="n">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D77" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="E77" s="1" t="n">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D78" s="1" t="n">
+        <v>190</v>
+      </c>
+      <c r="E78" s="1" t="n">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D79" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="E79" s="1" t="n">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D80" s="1" t="n">
+        <v>180</v>
+      </c>
+      <c r="E80" s="1" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D81" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="E81" s="1" t="n">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D82" s="1" t="n">
+        <v>180</v>
+      </c>
+      <c r="E82" s="1" t="n">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D83" s="1" t="n">
+        <v>210</v>
+      </c>
+      <c r="E83" s="1" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D84" s="1" t="n">
+        <v>180</v>
+      </c>
+      <c r="E84" s="1" t="n">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D85" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="E85" s="1" t="n">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.511805555555556" right="0.511805555555556" top="0.7875" bottom="0.7875" header="0.511811023622047" footer="0.511811023622047"/>

--- a/precos.xlsx
+++ b/precos.xlsx
@@ -1985,6 +1985,12 @@
       <c r="C86" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="D86" s="1" t="n">
+        <v>190</v>
+      </c>
+      <c r="E86" s="1" t="n">
+        <v>209</v>
+      </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="1" t="s">
@@ -1995,6 +2001,12 @@
       </c>
       <c r="C87" s="1" t="s">
         <v>11</v>
+      </c>
+      <c r="D87" s="1" t="n">
+        <v>210</v>
+      </c>
+      <c r="E87" s="1" t="n">
+        <v>230</v>
       </c>
     </row>
   </sheetData>
